--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 5.133,86</t>
-  </si>
-  <si>
-    <t>54.5</t>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 5.126,34</t>
+  </si>
+  <si>
+    <t>54.6</t>
   </si>
   <si>
     <t>31.6</t>
   </si>
   <si>
-    <t>5.46</t>
-  </si>
-  <si>
-    <t>19.3</t>
+    <t>5.57</t>
+  </si>
+  <si>
+    <t>19.2</t>
   </si>
   <si>
     <t>7.2</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>38.6%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>38.4%</t>
   </si>
   <si>
     <t>17.3%</t>
@@ -974,46 +974,46 @@
     <t>4.0%</t>
   </si>
   <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>1240.0</t>
-  </si>
-  <si>
-    <t>980.0</t>
-  </si>
-  <si>
-    <t>111.0</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>229.0</t>
-  </si>
-  <si>
-    <t>77.0</t>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>6.9%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>1270.0</t>
+  </si>
+  <si>
+    <t>1008.0</t>
+  </si>
+  <si>
+    <t>114.0</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>233.0</t>
+  </si>
+  <si>
+    <t>78.0</t>
   </si>
   <si>
     <t>15.0</t>
   </si>
   <si>
-    <t>397.0</t>
-  </si>
-  <si>
-    <t>150.0</t>
-  </si>
-  <si>
-    <t>238.0</t>
+    <t>401.0</t>
+  </si>
+  <si>
+    <t>158.0</t>
+  </si>
+  <si>
+    <t>248.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -3297,7 +3297,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3327,35 +3327,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>8705.6700000000001</v>
+      </c>
+      <c r="N13" s="6">
+        <v>93</v>
+      </c>
+      <c r="O13" s="6">
+        <v>67</v>
+      </c>
+      <c r="P13" s="7">
+        <v>7.6062500000000002</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>20.447264179104476</v>
+      </c>
+      <c r="R13" s="8">
+        <v>5.6674134328358212</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.28358208955223879</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.029850746268656716</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.14925373134328357</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>19</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>7</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -6724,7 +6782,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6754,35 +6812,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>4582.8500000000004</v>
+      </c>
+      <c r="N36" s="6">
+        <v>56</v>
+      </c>
+      <c r="O36" s="6">
+        <v>30</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.5070000000000006</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>18.731110000000001</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.503333333333333</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7606,7 +7722,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7636,35 +7752,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>3381.8299999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>40</v>
+      </c>
+      <c r="O42" s="6">
+        <v>30</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.0788609756097562</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>17.238890000000001</v>
+      </c>
+      <c r="R42" s="8">
+        <v>4.1600000000000001</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -11960,13 +12134,13 @@
         <v>0.48275862068965519</v>
       </c>
       <c r="U71" s="9">
-        <v>0.27586206896551724</v>
+        <v>0.31034482758620691</v>
       </c>
       <c r="V71" s="9">
         <v>0.034482758620689655</v>
       </c>
       <c r="W71" s="9">
-        <v>0</v>
+        <v>0.034482758619999998</v>
       </c>
       <c r="X71" s="9">
         <v>0.13793103448275862</v>
@@ -11990,13 +12164,13 @@
         <v>13</v>
       </c>
       <c r="AE71" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF71" s="6">
         <v>1</v>
       </c>
       <c r="AG71" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH71" s="6">
         <v>4</v>
@@ -14853,7 +15027,7 @@
         <v>19698</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C91" s="4">
         <v>51</v>
@@ -14883,35 +15057,93 @@
         <v>58</v>
       </c>
       <c r="L91" s="4"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="6"/>
-      <c r="O91" s="6"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="8"/>
-      <c r="R91" s="8"/>
-      <c r="S91" s="8"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
-      <c r="V91" s="9"/>
-      <c r="W91" s="9"/>
-      <c r="X91" s="9"/>
-      <c r="Y91" s="9"/>
-      <c r="Z91" s="9"/>
-      <c r="AA91" s="9"/>
-      <c r="AB91" s="9"/>
-      <c r="AC91" s="9"/>
-      <c r="AD91" s="6"/>
-      <c r="AE91" s="6"/>
-      <c r="AF91" s="6"/>
-      <c r="AG91" s="6"/>
-      <c r="AH91" s="6"/>
-      <c r="AI91" s="6"/>
-      <c r="AJ91" s="6"/>
-      <c r="AK91" s="6"/>
-      <c r="AL91" s="6"/>
-      <c r="AM91" s="6"/>
-      <c r="AN91" s="9"/>
-      <c r="AO91" s="6"/>
+      <c r="M91" s="5">
+        <v>4718.1999999999998</v>
+      </c>
+      <c r="N91" s="6">
+        <v>52</v>
+      </c>
+      <c r="O91" s="6">
+        <v>30</v>
+      </c>
+      <c r="P91" s="7">
+        <v>6.7411943396226413</v>
+      </c>
+      <c r="Q91" s="8">
+        <v>18.496109999999998</v>
+      </c>
+      <c r="R91" s="8">
+        <v>5.8605566666666666</v>
+      </c>
+      <c r="S91" s="8">
+        <v>7</v>
+      </c>
+      <c r="T91" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U91" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V91" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="W91" s="9">
+        <v>0</v>
+      </c>
+      <c r="X91" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="Y91" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="9">
+        <v>0.033333333333333333</v>
+      </c>
+      <c r="AB91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE91" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF91" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP91" s="4">
         <v>58</v>
       </c>
@@ -25091,7 +25323,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>51</v>
@@ -25121,35 +25353,91 @@
         <v>58</v>
       </c>
       <c r="L161" s="4"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="6"/>
-      <c r="O161" s="6"/>
-      <c r="P161" s="7"/>
-      <c r="Q161" s="8"/>
+      <c r="M161" s="5">
+        <v>2904.5999999999999</v>
+      </c>
+      <c r="N161" s="6">
+        <v>37</v>
+      </c>
+      <c r="O161" s="6">
+        <v>1</v>
+      </c>
+      <c r="P161" s="7">
+        <v>21.448611111111109</v>
+      </c>
+      <c r="Q161" s="8">
+        <v>1.3667</v>
+      </c>
       <c r="R161" s="8"/>
-      <c r="S161" s="8"/>
-      <c r="T161" s="9"/>
-      <c r="U161" s="9"/>
-      <c r="V161" s="9"/>
-      <c r="W161" s="9"/>
-      <c r="X161" s="9"/>
-      <c r="Y161" s="9"/>
-      <c r="Z161" s="9"/>
-      <c r="AA161" s="9"/>
-      <c r="AB161" s="9"/>
-      <c r="AC161" s="9"/>
-      <c r="AD161" s="6"/>
-      <c r="AE161" s="6"/>
-      <c r="AF161" s="6"/>
-      <c r="AG161" s="6"/>
-      <c r="AH161" s="6"/>
-      <c r="AI161" s="6"/>
-      <c r="AJ161" s="6"/>
-      <c r="AK161" s="6"/>
-      <c r="AL161" s="6"/>
-      <c r="AM161" s="6"/>
-      <c r="AN161" s="9"/>
-      <c r="AO161" s="6"/>
+      <c r="S161" s="8">
+        <v>5.2999999999999998</v>
+      </c>
+      <c r="T161" s="9">
+        <v>1</v>
+      </c>
+      <c r="U161" s="9">
+        <v>1</v>
+      </c>
+      <c r="V161" s="9">
+        <v>1</v>
+      </c>
+      <c r="W161" s="9">
+        <v>0</v>
+      </c>
+      <c r="X161" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y161" s="9">
+        <v>1</v>
+      </c>
+      <c r="Z161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK161" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM161" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN161" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO161" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP161" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 5.126,34</t>
-  </si>
-  <si>
-    <t>54.6</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 5.113,99</t>
+  </si>
+  <si>
+    <t>54.4</t>
   </si>
   <si>
     <t>31.6</t>
@@ -950,19 +950,19 @@
     <t>5.57</t>
   </si>
   <si>
-    <t>19.2</t>
-  </si>
-  <si>
-    <t>7.2</t>
+    <t>19.3</t>
+  </si>
+  <si>
+    <t>7.3</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>38.4%</t>
-  </si>
-  <si>
-    <t>17.3%</t>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>17.4%</t>
   </si>
   <si>
     <t>2.0%</t>
@@ -974,7 +974,7 @@
     <t>4.0%</t>
   </si>
   <si>
-    <t>1.3%</t>
+    <t>1.4%</t>
   </si>
   <si>
     <t>6.9%</t>
@@ -986,34 +986,34 @@
     <t>4.3%</t>
   </si>
   <si>
-    <t>1270.0</t>
-  </si>
-  <si>
-    <t>1008.0</t>
-  </si>
-  <si>
-    <t>114.0</t>
-  </si>
-  <si>
-    <t>19.0</t>
-  </si>
-  <si>
-    <t>233.0</t>
-  </si>
-  <si>
-    <t>78.0</t>
+    <t>1278.0</t>
+  </si>
+  <si>
+    <t>1014.0</t>
+  </si>
+  <si>
+    <t>115.0</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>234.0</t>
+  </si>
+  <si>
+    <t>79.0</t>
   </si>
   <si>
     <t>15.0</t>
   </si>
   <si>
-    <t>401.0</t>
+    <t>403.0</t>
   </si>
   <si>
     <t>158.0</t>
   </si>
   <si>
-    <t>248.0</t>
+    <t>251.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -16686,7 +16686,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16716,35 +16716,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>2854.4200000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>31</v>
+      </c>
+      <c r="O102" s="6">
+        <v>16</v>
+      </c>
+      <c r="P102" s="7">
+        <v>6.0130218749999997</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>39.402081250000002</v>
+      </c>
+      <c r="R102" s="8">
+        <v>29.359999999999999</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
@@ -932,40 +932,43 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
   </si>
   <si>
-    <t>30</t>
+    <t>215</t>
   </si>
   <si>
-    <t>R$ 5.113,99</t>
+    <t>29</t>
   </si>
   <si>
-    <t>54.4</t>
+    <t>R$ 5.123,77</t>
+  </si>
+  <si>
+    <t>54.5</t>
   </si>
   <si>
     <t>31.6</t>
   </si>
   <si>
-    <t>5.57</t>
+    <t>5.60</t>
   </si>
   <si>
     <t>19.3</t>
   </si>
   <si>
-    <t>7.3</t>
+    <t>7.2</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>38.3%</t>
+    <t>38.0%</t>
   </si>
   <si>
-    <t>17.4%</t>
+    <t>17.3%</t>
   </si>
   <si>
-    <t>2.0%</t>
+    <t>1.9%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -983,13 +986,13 @@
     <t>2.7%</t>
   </si>
   <si>
-    <t>4.3%</t>
+    <t>4.2%</t>
   </si>
   <si>
-    <t>1278.0</t>
+    <t>1304.0</t>
   </si>
   <si>
-    <t>1014.0</t>
+    <t>1030.0</t>
   </si>
   <si>
     <t>115.0</t>
@@ -998,28 +1001,28 @@
     <t>20.0</t>
   </si>
   <si>
-    <t>234.0</t>
+    <t>240.0</t>
   </si>
   <si>
-    <t>79.0</t>
+    <t>82.0</t>
   </si>
   <si>
-    <t>15.0</t>
+    <t>17.0</t>
   </si>
   <si>
-    <t>403.0</t>
+    <t>413.0</t>
   </si>
   <si>
-    <t>158.0</t>
+    <t>160.0</t>
   </si>
   <si>
-    <t>251.0</t>
+    <t>253.0</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>23.0</t>
+    <t>24.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6526,7 +6529,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6556,35 +6559,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>9726.3999999999996</v>
+      </c>
+      <c r="N34" s="6">
+        <v>94</v>
+      </c>
+      <c r="O34" s="6">
+        <v>52</v>
+      </c>
+      <c r="P34" s="7">
+        <v>11.513586956521738</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>20.89248431372549</v>
+      </c>
+      <c r="R34" s="8">
+        <v>3.7269999999999999</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.49019607843137253</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -18732,33 +18793,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>18</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22499,7 +22606,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22529,35 +22636,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>2320.6999999999998</v>
+      </c>
+      <c r="N141" s="6">
+        <v>24</v>
+      </c>
+      <c r="O141" s="6">
+        <v>11</v>
+      </c>
+      <c r="P141" s="7">
+        <v>4.2909708333333336</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>15.7697</v>
+      </c>
+      <c r="R141" s="8">
+        <v>2.4772727272727271</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33418,137 +33583,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>49</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0.061224489795918366</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.10204081632653061</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>1</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
-        <v>319</v>
-      </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>337</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>338</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>338</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
@@ -938,13 +938,13 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
+    <t>28</t>
   </si>
   <si>
-    <t>R$ 5.123,77</t>
+    <t>R$ 5.127,91</t>
   </si>
   <si>
-    <t>54.5</t>
+    <t>54.6</t>
   </si>
   <si>
     <t>31.6</t>
@@ -962,7 +962,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>38.0%</t>
+    <t>38.2%</t>
   </si>
   <si>
     <t>17.3%</t>
@@ -25250,7 +25250,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25280,18 +25280,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>5897.4300000000003</v>
+      </c>
+      <c r="N159" s="6">
+        <v>75</v>
+      </c>
       <c r="O159" s="6">
         <v>45</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>5.0100523809523816</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>20.787406666666666</v>
+      </c>
+      <c r="R159" s="8">
+        <v>8.7056818181818176</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.31111111111111112</v>
+      </c>
       <c r="U159" s="9">
         <v>0.17777777777777778</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>27</t>
   </si>
   <si>
-    <t>R$ 5.127,91</t>
+    <t>R$ 5.132,30</t>
   </si>
   <si>
     <t>54.6</t>
@@ -950,13 +950,13 @@
     <t>31.6</t>
   </si>
   <si>
-    <t>5.60</t>
+    <t>5.63</t>
   </si>
   <si>
     <t>19.3</t>
   </si>
   <si>
-    <t>7.2</t>
+    <t>7.3</t>
   </si>
   <si>
     <t>6.3</t>
@@ -14834,7 +14834,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14862,14 +14862,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>5952.6899999999996</v>
+      </c>
+      <c r="N89" s="6">
+        <v>56</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>12.360819298245614</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>34.279164999999999</v>
+      </c>
+      <c r="R89" s="8">
+        <v>13.717500000000001</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.050000000000000003</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29258,7 +29270,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31966,7 +31978,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33599,7 +33611,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-06).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>27</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 5.132,30</t>
+    <t>R$ 5.050,38</t>
   </si>
   <si>
-    <t>54.6</t>
+    <t>53.8</t>
   </si>
   <si>
-    <t>31.6</t>
+    <t>31.5</t>
   </si>
   <si>
-    <t>5.63</t>
+    <t>5.61</t>
   </si>
   <si>
-    <t>19.3</t>
+    <t>19.2</t>
   </si>
   <si>
-    <t>7.3</t>
+    <t>7.2</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
-    <t>38.2%</t>
+    <t>38.1%</t>
   </si>
   <si>
-    <t>17.3%</t>
+    <t>17.0%</t>
   </si>
   <si>
     <t>1.9%</t>
@@ -980,19 +980,19 @@
     <t>1.4%</t>
   </si>
   <si>
-    <t>6.9%</t>
+    <t>6.8%</t>
   </si>
   <si>
-    <t>2.7%</t>
+    <t>2.6%</t>
   </si>
   <si>
-    <t>4.2%</t>
+    <t>4.1%</t>
   </si>
   <si>
-    <t>1304.0</t>
+    <t>1312.0</t>
   </si>
   <si>
-    <t>1030.0</t>
+    <t>1036.0</t>
   </si>
   <si>
     <t>115.0</t>
@@ -1001,16 +1001,16 @@
     <t>20.0</t>
   </si>
   <si>
-    <t>240.0</t>
+    <t>243.0</t>
   </si>
   <si>
-    <t>82.0</t>
+    <t>83.0</t>
   </si>
   <si>
-    <t>17.0</t>
+    <t>19.0</t>
   </si>
   <si>
-    <t>413.0</t>
+    <t>415.0</t>
   </si>
   <si>
     <t>160.0</t>
@@ -9190,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9220,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>769.70000000000005</v>
+      </c>
+      <c r="N51" s="6">
+        <v>9</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>3.1111111111111112</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>14.75835</v>
+      </c>
+      <c r="R51" s="8">
+        <v>15.85</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.5</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10259,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>52</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24182,7 +24240,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24212,35 +24270,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2257.04</v>
+      </c>
+      <c r="N151" s="6">
+        <v>33</v>
+      </c>
+      <c r="O151" s="6">
+        <v>26</v>
+      </c>
+      <c r="P151" s="7">
+        <v>3.8411468750000002</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>13.364103846153846</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.4910269230769231</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25064,7 +25180,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25094,35 +25210,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>2398.7600000000002</v>
+      </c>
+      <c r="N157" s="6">
+        <v>26</v>
+      </c>
+      <c r="O157" s="6">
+        <v>20</v>
+      </c>
+      <c r="P157" s="7">
+        <v>6.2925925925925927</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>16.82</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.271665</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25163,7 +25337,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25193,35 +25367,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2082.6900000000001</v>
+      </c>
+      <c r="N158" s="6">
+        <v>23</v>
+      </c>
+      <c r="O158" s="6">
+        <v>19</v>
+      </c>
+      <c r="P158" s="7">
+        <v>6.8969681818181821</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>17.068421052631578</v>
+      </c>
+      <c r="R158" s="8">
+        <v>2.8096473684210523</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.47368421052631576</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26196,7 +26428,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26226,35 +26458,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>2343.0999999999999</v>
+      </c>
+      <c r="N165" s="6">
+        <v>27</v>
+      </c>
+      <c r="O165" s="6">
+        <v>17</v>
+      </c>
+      <c r="P165" s="7">
+        <v>4.3746925925925924</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>14.901958823529412</v>
+      </c>
+      <c r="R165" s="8">
+        <v>3.5725470588235293</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
